--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,12 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615723.9331070933</v>
+        <v>615724</v>
       </c>
       <c r="R3" t="n">
-        <v>6685647.591231957</v>
+        <v>6685648</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -888,19 +883,9 @@
           <t>1995-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,12 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615823.7895882174</v>
+        <v>615824</v>
       </c>
       <c r="R4" t="n">
-        <v>6685648.778172389</v>
+        <v>6685649</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1014,19 +994,9 @@
           <t>1995-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1995-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101885</v>
+        <v>101893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101893</v>
+        <v>101898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101898</v>
+        <v>101904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101904</v>
+        <v>101905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101905</v>
+        <v>101932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101932</v>
+        <v>101938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101938</v>
+        <v>101945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101945</v>
+        <v>101949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101949</v>
+        <v>101956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101959</v>
+        <v>101964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -818,7 +818,7 @@
         <v>99119860</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>99119874</v>
       </c>
       <c r="B4" t="n">
-        <v>101964</v>
+        <v>101972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>86543639</v>
       </c>
       <c r="B2" t="n">
-        <v>95597</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616025.1844195669</v>
+        <v>616025</v>
       </c>
       <c r="R2" t="n">
-        <v>6685551.48290956</v>
+        <v>6685551</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,19 +757,9 @@
           <t>1995-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -815,27 +800,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99119860</v>
+        <v>99119874</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221343</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -846,14 +831,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sevallbo, 1 km SO Gundbo gruvor, Gstr</t>
+          <t>Sevallbo, Gundbo, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615724</v>
+        <v>615824</v>
       </c>
       <c r="R3" t="n">
-        <v>6685648</v>
+        <v>6685649</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -899,12 +884,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Berg, Hällmark, flacka hällar omgivna av tallungskog, torrt, i renlavmattor på N-exponerad häll.</t>
+          <t>Kulturmark, gammal skogsväg nu mer som körväg, ung gles tallskog, mager sandig mark, vatten rinner i grus.hjulspår v.reg</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 125840N</t>
+          <t>Gst Fyndnr 125826N</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,27 +911,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99119874</v>
+        <v>99119860</v>
       </c>
       <c r="B4" t="n">
-        <v>101972</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221343</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,14 +942,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sevallbo, Gundbo, Gstr</t>
+          <t>Sevallbo, 1 km SO Gundbo gruvor, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615824</v>
+        <v>615724</v>
       </c>
       <c r="R4" t="n">
-        <v>6685649</v>
+        <v>6685648</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1010,12 +995,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kulturmark, gammal skogsväg nu mer som körväg, ung gles tallskog, mager sandig mark, vatten rinner i grus.hjulspår v.reg</t>
+          <t>Berg, Hällmark, flacka hällar omgivna av tallungskog, torrt, i renlavmattor på N-exponerad häll.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 125826N</t>
+          <t>Gst Fyndnr 125840N</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 29626-2025 artfynd.xlsx
+++ b/artfynd/A 29626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86543639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99119874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,8 +1034,18 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99119860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>